--- a/AAII_Financials/Quarterly/MMEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MMEX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>MMEX</t>
   </si>
@@ -656,136 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -873,8 +881,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,8 +976,14 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1071,14 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,20 +1296,26 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1286,23 +1326,23 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1322,37 +1362,43 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-500</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-200</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,97 +1522,105 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E17" s="3">
         <v>300</v>
       </c>
       <c r="F17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>300</v>
+      </c>
+      <c r="H17" s="3">
         <v>200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>-200</v>
-      </c>
-      <c r="N17" s="3">
-        <v>200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>500</v>
       </c>
       <c r="P17" s="3">
         <v>200</v>
       </c>
       <c r="Q17" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="R17" s="3">
         <v>200</v>
       </c>
       <c r="S17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="T17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U17" s="3">
         <v>400</v>
       </c>
       <c r="V17" s="3">
+        <v>300</v>
+      </c>
+      <c r="W17" s="3">
+        <v>400</v>
+      </c>
+      <c r="X17" s="3">
         <v>500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>-200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1571,85 +1631,91 @@
         <v>-300</v>
       </c>
       <c r="F18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-500</v>
       </c>
       <c r="P18" s="3">
         <v>-200</v>
       </c>
       <c r="Q18" s="3">
-        <v>-200</v>
+        <v>-500</v>
       </c>
       <c r="R18" s="3">
         <v>-200</v>
       </c>
       <c r="S18" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="T18" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="U18" s="3">
         <v>-400</v>
       </c>
       <c r="V18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1747,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1711,67 +1779,73 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-24100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-800</v>
       </c>
       <c r="S20" s="3">
         <v>-400</v>
       </c>
       <c r="T20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>4500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,88 +1853,94 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-23900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>4300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1868,61 +1948,61 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
       <c r="I22" s="3">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>100</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
       </c>
       <c r="O22" s="3">
+        <v>200</v>
+      </c>
+      <c r="P22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>500</v>
-      </c>
-      <c r="T22" s="3">
-        <v>700</v>
       </c>
       <c r="U22" s="3">
         <v>500</v>
       </c>
       <c r="V22" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="W22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X22" s="3">
         <v>400</v>
@@ -1931,114 +2011,126 @@
         <v>600</v>
       </c>
       <c r="Z22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>300</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>100</v>
       </c>
       <c r="AE22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-24100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-24100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>4000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-24100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y27" s="3">
         <v>-1100</v>
       </c>
       <c r="Z27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>4000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2883,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2779,156 +2919,168 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>24100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>800</v>
       </c>
       <c r="S32" s="3">
         <v>400</v>
       </c>
       <c r="T32" s="3">
+        <v>800</v>
+      </c>
+      <c r="U32" s="3">
+        <v>400</v>
+      </c>
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>6400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-24100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y33" s="3">
         <v>-1100</v>
       </c>
       <c r="Z33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>4000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-24100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y35" s="3">
         <v>-1100</v>
       </c>
       <c r="Z35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>4000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3437,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3286,31 +3460,31 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
-      </c>
-      <c r="K41" s="3">
-        <v>300</v>
-      </c>
-      <c r="L41" s="3">
-        <v>1700</v>
       </c>
       <c r="M41" s="3">
         <v>300</v>
       </c>
       <c r="N41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O41" s="3">
+        <v>300</v>
+      </c>
+      <c r="P41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R41" s="3">
         <v>0</v>
@@ -3325,25 +3499,25 @@
         <v>100</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
+        <v>100</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
-      </c>
-      <c r="W41" s="3">
-        <v>300</v>
-      </c>
-      <c r="X41" s="3">
-        <v>0</v>
       </c>
       <c r="Y41" s="3">
         <v>300</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB41" s="3">
         <v>100</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>0</v>
       </c>
       <c r="AC41" s="3">
         <v>100</v>
@@ -3352,10 +3526,16 @@
         <v>0</v>
       </c>
       <c r="AE41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3623,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3532,8 +3718,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3813,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3636,29 +3834,29 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
@@ -3695,11 +3893,11 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>4</v>
@@ -3710,8 +3908,14 @@
       <c r="AE45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3725,37 +3929,37 @@
         <v>0</v>
       </c>
       <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
         <v>100</v>
       </c>
-      <c r="H46" s="3">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
         <v>200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R46" s="3">
         <v>0</v>
@@ -3770,25 +3974,25 @@
         <v>100</v>
       </c>
       <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
+        <v>100</v>
+      </c>
+      <c r="X46" s="3">
         <v>200</v>
-      </c>
-      <c r="W46" s="3">
-        <v>300</v>
-      </c>
-      <c r="X46" s="3">
-        <v>0</v>
       </c>
       <c r="Y46" s="3">
         <v>300</v>
       </c>
       <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB46" s="3">
         <v>100</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>0</v>
       </c>
       <c r="AC46" s="3">
         <v>100</v>
@@ -3797,10 +4001,16 @@
         <v>0</v>
       </c>
       <c r="AE46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +4098,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3912,19 +4128,19 @@
         <v>1100</v>
       </c>
       <c r="J48" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="K48" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="L48" s="3">
         <v>700</v>
       </c>
       <c r="M48" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N48" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="O48" s="3">
         <v>500</v>
@@ -3948,37 +4164,43 @@
         <v>500</v>
       </c>
       <c r="V48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W48" s="3">
         <v>500</v>
       </c>
       <c r="X48" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z48" s="3">
         <v>300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>300</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>100</v>
       </c>
       <c r="AB48" s="3">
         <v>100</v>
       </c>
       <c r="AC48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,25 +4478,31 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -4324,17 +4564,23 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4668,14 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4437,37 +4689,37 @@
         <v>1100</v>
       </c>
       <c r="G54" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H54" s="3">
         <v>1100</v>
       </c>
       <c r="I54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K54" s="3">
         <v>1300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>800</v>
-      </c>
-      <c r="N54" s="3">
-        <v>500</v>
-      </c>
-      <c r="O54" s="3">
-        <v>500</v>
       </c>
       <c r="P54" s="3">
         <v>500</v>
       </c>
       <c r="Q54" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R54" s="3">
         <v>500</v>
@@ -4476,43 +4728,49 @@
         <v>600</v>
       </c>
       <c r="T54" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U54" s="3">
         <v>600</v>
       </c>
       <c r="V54" s="3">
+        <v>600</v>
+      </c>
+      <c r="W54" s="3">
+        <v>600</v>
+      </c>
+      <c r="X54" s="3">
         <v>700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>100</v>
       </c>
-      <c r="AD54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,102 +4837,110 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>800</v>
-      </c>
-      <c r="R57" s="3">
-        <v>900</v>
       </c>
       <c r="S57" s="3">
         <v>800</v>
       </c>
       <c r="T57" s="3">
+        <v>900</v>
+      </c>
+      <c r="U57" s="3">
+        <v>800</v>
+      </c>
+      <c r="V57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>700</v>
       </c>
       <c r="AA57" s="3">
         <v>700</v>
       </c>
       <c r="AB57" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AC57" s="3">
         <v>700</v>
       </c>
       <c r="AD57" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AE57" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="E58" s="3">
         <v>1800</v>
@@ -4681,73 +4949,73 @@
         <v>1800</v>
       </c>
       <c r="G58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>600</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>400</v>
       </c>
       <c r="AA58" s="3">
         <v>500</v>
       </c>
       <c r="AB58" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AC58" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD58" s="3">
         <v>600</v>
@@ -4755,8 +5023,14 @@
       <c r="AE58" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4770,171 +5044,183 @@
         <v>1000</v>
       </c>
       <c r="G59" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H59" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="3">
         <v>900</v>
       </c>
       <c r="J59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L59" s="3">
         <v>800</v>
       </c>
       <c r="M59" s="3">
+        <v>800</v>
+      </c>
+      <c r="N59" s="3">
+        <v>800</v>
+      </c>
+      <c r="O59" s="3">
         <v>3800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2700</v>
-      </c>
-      <c r="P59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>3400</v>
       </c>
       <c r="R59" s="3">
         <v>2600</v>
       </c>
       <c r="S59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>7700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>5200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>9000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4987,16 +5273,16 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>100</v>
       </c>
       <c r="W61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X61" s="3">
         <v>100</v>
@@ -5008,10 +5294,10 @@
         <v>100</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -5022,8 +5308,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5111,8 +5403,14 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>6100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3400</v>
-      </c>
-      <c r="X66" s="3">
-        <v>2700</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>2600</v>
       </c>
       <c r="Z66" s="3">
         <v>2700</v>
       </c>
       <c r="AA66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AC66" s="3">
         <v>3500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>8600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-74800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-74300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-73900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-72700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-72400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-72100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-71600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-68200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-67500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-66800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-65700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-68000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-43900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-43400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-43500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-42400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-41100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-39800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-39100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-38600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-37200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-35100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-33700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-32900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-36900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-30100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-30400</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-3000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-2900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-2700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-2500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-2000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-1100</v>
       </c>
       <c r="K76" s="3">
         <v>-1800</v>
       </c>
       <c r="L76" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M76" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N76" s="3">
         <v>-800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-5800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-5800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-5600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-5700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-4700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-4200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-3300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-3400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-3500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-2500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-24100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y81" s="3">
         <v>-1100</v>
       </c>
       <c r="Z81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>4000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +7093,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,49 +7568,55 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
         <v>-100</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-100</v>
       </c>
       <c r="Q89" s="3">
         <v>-100</v>
@@ -7191,46 +7625,52 @@
         <v>-100</v>
       </c>
       <c r="S89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-300</v>
       </c>
       <c r="AB89" s="3">
         <v>-300</v>
       </c>
       <c r="AC89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7283,34 +7725,34 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7324,35 +7766,41 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7983,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7550,23 +8010,23 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -7592,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -7604,22 +8064,28 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8493,109 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E100" s="3">
         <v>100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
+        <v>100</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
-      </c>
-      <c r="W100" s="3">
-        <v>1000</v>
-      </c>
-      <c r="X100" s="3">
-        <v>100</v>
       </c>
       <c r="Y100" s="3">
         <v>1000</v>
       </c>
       <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8683,14 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8203,34 +8707,34 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>100</v>
       </c>
       <c r="R102" s="3">
         <v>-100</v>
@@ -8242,36 +8746,42 @@
         <v>-100</v>
       </c>
       <c r="U102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="V102" s="3">
         <v>-100</v>
       </c>
       <c r="W102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MMEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MMEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>MMEX</t>
   </si>
@@ -2324,8 +2324,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-400</v>
       </c>
       <c r="E26" s="3">
         <v>-400</v>
@@ -2419,8 +2419,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-400</v>
       </c>
       <c r="E27" s="3">
         <v>-400</v>
@@ -2989,8 +2989,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-400</v>
       </c>
       <c r="E33" s="3">
         <v>-400</v>
@@ -3179,8 +3179,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-400</v>
       </c>
       <c r="E35" s="3">
         <v>-400</v>
@@ -6590,7 +6590,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-3500</v>
+        <v>-3600</v>
       </c>
       <c r="E76" s="3">
         <v>-3200</v>
@@ -6879,8 +6879,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-400</v>
       </c>
       <c r="E81" s="3">
         <v>-400</v>

--- a/AAII_Financials/Quarterly/MMEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MMEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>MMEX</t>
   </si>
@@ -656,144 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -887,8 +894,14 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +995,14 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1096,14 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,17 +1350,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -1332,23 +1371,23 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1368,37 +1407,43 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-500</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-200</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,103 +1575,111 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>400</v>
+      </c>
+      <c r="F17" s="3">
         <v>300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1100</v>
       </c>
       <c r="G17" s="3">
         <v>300</v>
       </c>
       <c r="H17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>300</v>
+      </c>
+      <c r="J17" s="3">
         <v>200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>-200</v>
-      </c>
-      <c r="P17" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>500</v>
       </c>
       <c r="R17" s="3">
         <v>200</v>
       </c>
       <c r="S17" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="T17" s="3">
         <v>200</v>
       </c>
       <c r="U17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="V17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W17" s="3">
         <v>400</v>
       </c>
       <c r="X17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>-200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,94 +1687,100 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1100</v>
       </c>
       <c r="G18" s="3">
         <v>-300</v>
       </c>
       <c r="H18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-500</v>
       </c>
       <c r="R18" s="3">
         <v>-200</v>
       </c>
       <c r="S18" s="3">
-        <v>-200</v>
+        <v>-500</v>
       </c>
       <c r="T18" s="3">
         <v>-200</v>
       </c>
       <c r="U18" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="V18" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="W18" s="3">
         <v>-400</v>
       </c>
       <c r="X18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1814,10 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1785,67 +1852,73 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-24100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-800</v>
       </c>
       <c r="U20" s="3">
         <v>-400</v>
       </c>
       <c r="V20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>4500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1853,94 +1926,100 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-23900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>4300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,67 +2027,67 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
       <c r="K22" s="3">
+        <v>100</v>
+      </c>
+      <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
       </c>
       <c r="Q22" s="3">
+        <v>200</v>
+      </c>
+      <c r="R22" s="3">
+        <v>200</v>
+      </c>
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>500</v>
-      </c>
-      <c r="V22" s="3">
-        <v>700</v>
       </c>
       <c r="W22" s="3">
         <v>500</v>
       </c>
       <c r="X22" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="Y22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Z22" s="3">
         <v>400</v>
@@ -2017,120 +2096,132 @@
         <v>600</v>
       </c>
       <c r="AB22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC22" s="3">
         <v>600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE22" s="3">
         <v>400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>300</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>100</v>
       </c>
       <c r="AG22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="E23" s="3">
         <v>-400</v>
       </c>
       <c r="F23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-24100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>4000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-400</v>
+      <c r="D26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E26" s="3">
         <v>-400</v>
       </c>
       <c r="F26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-24100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>4000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-24100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA27" s="3">
         <v>-1100</v>
       </c>
       <c r="AB27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>4000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +3022,14 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2925,162 +3064,174 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>24100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>800</v>
       </c>
       <c r="U32" s="3">
         <v>400</v>
       </c>
       <c r="V32" s="3">
+        <v>800</v>
+      </c>
+      <c r="W32" s="3">
+        <v>400</v>
+      </c>
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>6400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-24100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA33" s="3">
         <v>-1100</v>
       </c>
       <c r="AB33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>4000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-24100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA35" s="3">
         <v>-1100</v>
       </c>
       <c r="AB35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>4000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,8 +3610,10 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3466,31 +3639,31 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
-      </c>
-      <c r="M41" s="3">
-        <v>300</v>
-      </c>
-      <c r="N41" s="3">
-        <v>1700</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
       </c>
       <c r="P41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>300</v>
+      </c>
+      <c r="R41" s="3">
         <v>100</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -3505,25 +3678,25 @@
         <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>0</v>
       </c>
       <c r="AA41" s="3">
         <v>300</v>
       </c>
       <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD41" s="3">
         <v>100</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>0</v>
       </c>
       <c r="AE41" s="3">
         <v>100</v>
@@ -3532,10 +3705,16 @@
         <v>0</v>
       </c>
       <c r="AG41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,8 +3808,14 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3909,14 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +4010,14 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3840,29 +4037,29 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3899,11 +4096,11 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>4</v>
@@ -3914,8 +4111,14 @@
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3935,37 +4138,37 @@
         <v>0</v>
       </c>
       <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3">
-        <v>0</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3">
         <v>200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3">
         <v>0</v>
@@ -3980,25 +4183,25 @@
         <v>100</v>
       </c>
       <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z46" s="3">
         <v>200</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>0</v>
       </c>
       <c r="AA46" s="3">
         <v>300</v>
       </c>
       <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD46" s="3">
         <v>100</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>0</v>
       </c>
       <c r="AE46" s="3">
         <v>100</v>
@@ -4007,10 +4210,16 @@
         <v>0</v>
       </c>
       <c r="AG46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,16 +4313,22 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="E48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F48" s="3">
         <v>1100</v>
@@ -4134,19 +4349,19 @@
         <v>1100</v>
       </c>
       <c r="L48" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="M48" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="N48" s="3">
         <v>700</v>
       </c>
       <c r="O48" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="P48" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="Q48" s="3">
         <v>500</v>
@@ -4170,37 +4385,43 @@
         <v>500</v>
       </c>
       <c r="X48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Y48" s="3">
         <v>500</v>
       </c>
       <c r="Z48" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB48" s="3">
         <v>300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>300</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>100</v>
       </c>
       <c r="AD48" s="3">
         <v>100</v>
       </c>
       <c r="AE48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4717,14 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4570,17 +4809,23 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,16 +4919,22 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E54" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F54" s="3">
         <v>1100</v>
@@ -4695,37 +4946,37 @@
         <v>1100</v>
       </c>
       <c r="I54" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="J54" s="3">
         <v>1100</v>
       </c>
       <c r="K54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L54" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M54" s="3">
         <v>1300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>800</v>
-      </c>
-      <c r="P54" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>500</v>
       </c>
       <c r="R54" s="3">
         <v>500</v>
       </c>
       <c r="S54" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T54" s="3">
         <v>500</v>
@@ -4734,43 +4985,49 @@
         <v>600</v>
       </c>
       <c r="V54" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W54" s="3">
         <v>600</v>
       </c>
       <c r="X54" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z54" s="3">
         <v>700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>100</v>
       </c>
-      <c r="AF54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,114 +5098,122 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
-      </c>
-      <c r="S57" s="3">
-        <v>800</v>
-      </c>
-      <c r="T57" s="3">
-        <v>900</v>
       </c>
       <c r="U57" s="3">
         <v>800</v>
       </c>
       <c r="V57" s="3">
+        <v>900</v>
+      </c>
+      <c r="W57" s="3">
+        <v>800</v>
+      </c>
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>700</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>700</v>
       </c>
       <c r="AC57" s="3">
         <v>700</v>
       </c>
       <c r="AD57" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AE57" s="3">
         <v>700</v>
       </c>
       <c r="AF57" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AG57" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1900</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1800</v>
       </c>
       <c r="G58" s="3">
         <v>1800</v>
@@ -4955,73 +5222,73 @@
         <v>1800</v>
       </c>
       <c r="I58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>600</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>400</v>
       </c>
       <c r="AC58" s="3">
         <v>500</v>
       </c>
       <c r="AD58" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AE58" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AF58" s="3">
         <v>600</v>
@@ -5029,8 +5296,14 @@
       <c r="AG58" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5038,7 +5311,7 @@
         <v>1000</v>
       </c>
       <c r="E59" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F59" s="3">
         <v>1000</v>
@@ -5050,182 +5323,194 @@
         <v>1000</v>
       </c>
       <c r="I59" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J59" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="K59" s="3">
         <v>900</v>
       </c>
       <c r="L59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="M59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N59" s="3">
         <v>800</v>
       </c>
       <c r="O59" s="3">
+        <v>800</v>
+      </c>
+      <c r="P59" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="S59" s="3">
-        <v>3400</v>
       </c>
       <c r="T59" s="3">
         <v>2600</v>
       </c>
       <c r="U59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="W59" s="3">
         <v>1900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>7700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>5900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>6300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>4000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>3300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>9000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5279,16 +5564,16 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>100</v>
       </c>
       <c r="Y61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z61" s="3">
         <v>100</v>
@@ -5300,10 +5585,10 @@
         <v>100</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
@@ -5314,8 +5599,14 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5409,8 +5700,14 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>6600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>6300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>4200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3400</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>2600</v>
       </c>
       <c r="AB66" s="3">
         <v>2700</v>
       </c>
       <c r="AC66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE66" s="3">
         <v>3500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>8600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-81400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-74800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-74300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-73900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-72700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-72400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-72100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-71600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-68200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-67500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-66800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-65700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-68000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-43900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-43400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-43100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-43500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-42400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-41100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-39800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-39100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-38600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-36100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-34000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-32900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-36900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-30100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-30400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-3600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-3200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-3000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-2900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-2700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-2500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-1100</v>
       </c>
       <c r="M76" s="3">
         <v>-1800</v>
       </c>
       <c r="N76" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O76" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P76" s="3">
         <v>-800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-5800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-5600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-5300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-5700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-4700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-4200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-3300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-3400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-24100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA81" s="3">
         <v>-1100</v>
       </c>
       <c r="AB81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>4000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7399,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7099,8 +7496,14 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,55 +8001,61 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>-100</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G89" s="3">
         <v>-100</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-100</v>
       </c>
       <c r="S89" s="3">
         <v>-100</v>
@@ -7631,46 +8064,52 @@
         <v>-100</v>
       </c>
       <c r="U89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-300</v>
       </c>
       <c r="AD89" s="3">
         <v>-300</v>
       </c>
       <c r="AE89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +8143,10 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7731,34 +8172,34 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -7772,35 +8213,41 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8442,14 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8016,23 +8475,23 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -8058,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -8070,22 +8529,28 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8984,115 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>100</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G100" s="3">
         <v>100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3">
+        <v>100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>100</v>
       </c>
       <c r="AA100" s="3">
         <v>1000</v>
       </c>
       <c r="AB100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,8 +9186,14 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8713,34 +9216,34 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S102" s="3">
-        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>-100</v>
@@ -8752,36 +9255,42 @@
         <v>-100</v>
       </c>
       <c r="W102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X102" s="3">
         <v>-100</v>
       </c>
       <c r="Y102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
